--- a/astro-site/public/dl/haccp-templates/BONUS-02-food-recall-response-plan.xlsx
+++ b/astro-site/public/dl/haccp-templates/BONUS-02-food-recall-response-plan.xlsx
@@ -680,7 +680,7 @@
     <row r="8">
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>▸ Go over the seven steps with the whole team and note it in the training log (BONUS-01 (Food Safety Training Log)).</t>
+          <t>▸ Go over the seven steps with the whole team and note it in the training log, BONUS-01 (Food Safety Training Log).</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>Check template 06 (Food Traceability Log (Lots In &amp; Out)) (lots in and out).</t>
+          <t>Check template 06 (Food Traceability Log), lots in and out.</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>Complete the corrective action log (template 11 (Corrective Action Log)) with the incident number.</t>
+          <t>Complete the corrective action log in template 11 (Corrective Action Log) with the incident number.</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>File it with the corrective action log (template 11 (Corrective Action Log)) and review whether any procedure has to change so it does not happen again.</t>
+          <t>File it with the corrective action log in template 11 (Corrective Action Log) and review whether any procedure has to change so it does not happen again.</t>
         </is>
       </c>
     </row>
